--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.555422964762332</v>
+        <v>1.065256231773879</v>
       </c>
       <c r="D2" t="n">
-        <v>6.485377052874639</v>
+        <v>1.053873771092129</v>
       </c>
       <c r="E2" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F2" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.905865990715781</v>
+        <v>1.284703223491314</v>
       </c>
       <c r="D3" t="n">
-        <v>7.581228561371275</v>
+        <v>1.231949641222832</v>
       </c>
       <c r="E3" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F3" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.95234852953411</v>
+        <v>6.654756636049292</v>
       </c>
       <c r="D4" t="n">
-        <v>40.47819687874202</v>
+        <v>6.577706992795578</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F4" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.54683399680098</v>
+        <v>5.12636052448016</v>
       </c>
       <c r="D5" t="n">
-        <v>31.4097386693839</v>
+        <v>5.104082533774884</v>
       </c>
       <c r="E5" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F5" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.99116566709072</v>
+        <v>2.761064420902241</v>
       </c>
       <c r="D6" t="n">
-        <v>17.01496235513009</v>
+        <v>2.764931382708641</v>
       </c>
       <c r="E6" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F6" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.72124153064362</v>
+        <v>3.042201748729588</v>
       </c>
       <c r="D7" t="n">
-        <v>20.25182175065734</v>
+        <v>3.290921034481818</v>
       </c>
       <c r="E7" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F7" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.74598932073279</v>
+        <v>3.696223264619078</v>
       </c>
       <c r="D8" t="n">
-        <v>22.2111097972061</v>
+        <v>3.609305342045991</v>
       </c>
       <c r="E8" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F8" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.44750015044661</v>
+        <v>5.760218774447574</v>
       </c>
       <c r="D9" t="n">
-        <v>26.27620909436867</v>
+        <v>4.269883977834909</v>
       </c>
       <c r="E9" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F9" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.07824557197901</v>
+        <v>7.000214905446589</v>
       </c>
       <c r="D10" t="n">
-        <v>11.4831712752637</v>
+        <v>1.866015332230351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.79863083080506</v>
+        <v>2.079777510005823</v>
       </c>
       <c r="F10" t="n">
-        <v>10.59909681091203</v>
+        <v>1.722353231773205</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
